--- a/plans/ml-intro.xlsx
+++ b/plans/ml-intro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\auto-ai\repositories\cabrerac.github.io\plans\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B26B86E4-8662-46A7-AC4A-241084F8AC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2F8C92-C5B8-44D2-8761-850E6B2914B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{097AC0F9-9204-4B6F-9000-8F1C4FC0E512}"/>
   </bookViews>
@@ -59,9 +59,6 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Data Management</t>
-  </si>
-  <si>
     <t>Compute</t>
   </si>
   <si>
@@ -94,9 +91,6 @@
 ML Project</t>
   </si>
   <si>
-    <t>Presentations</t>
-  </si>
-  <si>
     <t>Neural Networks and 
 Deep Learning</t>
   </si>
@@ -121,10 +115,17 @@
 Assessing methods</t>
   </si>
   <si>
-    <t>Offline processing
-Online processing
+    <t>Project presentations</t>
+  </si>
+  <si>
+    <t>Data Storing and 
+Processing</t>
+  </si>
+  <si>
+    <t>Data Architectures
 Storing data
-Architectures</t>
+Offline processing
+Online processing</t>
   </si>
 </sst>
 </file>
@@ -156,7 +157,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -179,11 +180,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -195,6 +207,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -558,7 +573,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -569,10 +584,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
@@ -582,8 +597,8 @@
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>23</v>
@@ -597,11 +612,11 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -609,11 +624,11 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -621,13 +636,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -635,13 +650,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -649,23 +664,23 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>19</v>
+      <c r="B10" s="5" t="s">
+        <v>8</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -673,10 +688,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>5</v>
